--- a/Lab2/in_class_work/Lab2_form_inClass.xlsx
+++ b/Lab2/in_class_work/Lab2_form_inClass.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maraielciu/Desktop/SSVV/Lab2/in_class_work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A08A5AAB-9C21-AD46-A808-CEBE1A63A85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5748F70D-4D5B-494E-87FF-F4B7FAC19672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Problem" sheetId="1" r:id="rId1"/>
@@ -51,6 +51,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Author:
@@ -65,6 +66,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Author:
@@ -77,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="153">
   <si>
     <t xml:space="preserve">Statement: </t>
   </si>
@@ -536,6 +538,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">TCs </t>
     </r>
@@ -545,6 +548,7 @@
         <sz val="11"/>
         <color rgb="FF008000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>passed</t>
     </r>
@@ -556,6 +560,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">TCs    </t>
     </r>
@@ -565,6 +570,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>failed</t>
     </r>
@@ -585,6 +591,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">TCs </t>
     </r>
@@ -594,6 +601,7 @@
         <sz val="11"/>
         <color rgb="FF008000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>passed</t>
     </r>
@@ -605,6 +613,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">TCs    </t>
     </r>
@@ -614,6 +623,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>failed</t>
     </r>
@@ -623,9 +633,6 @@
   </si>
   <si>
     <t>no</t>
-  </si>
-  <si>
-    <t>not yet</t>
   </si>
 </sst>
 </file>
@@ -635,7 +642,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\,\ m"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -646,11 +653,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -658,37 +667,51 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF31859B"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1404,15 +1427,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1451,6 +1474,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1458,26 +1496,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2754,7 +2777,7 @@
     <col min="6" max="26" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:5" ht="15" x14ac:dyDescent="0.2">
       <c r="B2" s="8" t="s">
         <v>11</v>
       </c>
@@ -2768,11 +2791,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="52" t="s">
         <v>16</v>
       </c>
       <c r="D3" s="7" t="s">
@@ -2780,106 +2803,106 @@
       </c>
       <c r="E3" s="9"/>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="51"/>
+      <c r="C4" s="53"/>
       <c r="D4" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="52"/>
+      <c r="C5" s="51"/>
       <c r="D5" s="8"/>
       <c r="E5" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="52" t="s">
         <v>23</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="53"/>
+      <c r="E6" s="54"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B7" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="51"/>
+      <c r="C7" s="53"/>
       <c r="D7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="52"/>
+      <c r="E7" s="51"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B8" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="51"/>
+      <c r="C8" s="53"/>
       <c r="D8" s="7" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="8"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="52"/>
+      <c r="C9" s="51"/>
       <c r="D9" s="8"/>
       <c r="E9" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:5" ht="15" x14ac:dyDescent="0.2">
       <c r="B10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:5" ht="15" x14ac:dyDescent="0.2">
       <c r="B11" s="8"/>
-      <c r="C11" s="54"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:5" ht="15" x14ac:dyDescent="0.2">
       <c r="B12" s="8"/>
-      <c r="C12" s="52"/>
+      <c r="C12" s="51"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:5" ht="15" x14ac:dyDescent="0.2">
       <c r="B13" s="8"/>
-      <c r="C13" s="54"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:5" ht="15" x14ac:dyDescent="0.2">
       <c r="B14" s="8"/>
-      <c r="C14" s="52"/>
+      <c r="C14" s="51"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:5" ht="15" x14ac:dyDescent="0.2">
       <c r="B15" s="8"/>
-      <c r="C15" s="54"/>
+      <c r="C15" s="50"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:5" ht="15" x14ac:dyDescent="0.2">
       <c r="B16" s="8"/>
-      <c r="C16" s="52"/>
+      <c r="C16" s="51"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
     </row>
@@ -3876,7 +3899,7 @@
       <c r="B3" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="52"/>
+      <c r="C3" s="51"/>
       <c r="D3" s="8" t="s">
         <v>35</v>
       </c>
@@ -6252,7 +6275,7 @@
       <c r="B4" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="52"/>
+      <c r="C4" s="51"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="40" t="s">
@@ -6287,7 +6310,7 @@
       <c r="B6" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="51"/>
+      <c r="C6" s="53"/>
       <c r="D6" s="18">
         <v>1</v>
       </c>
@@ -6305,7 +6328,7 @@
       <c r="B7" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="51"/>
+      <c r="C7" s="53"/>
       <c r="D7" s="18">
         <v>1</v>
       </c>
@@ -6323,7 +6346,7 @@
       <c r="B8" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="51"/>
+      <c r="C8" s="53"/>
       <c r="D8" s="18">
         <v>2</v>
       </c>
@@ -6341,7 +6364,7 @@
       <c r="B9" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="51"/>
+      <c r="C9" s="53"/>
       <c r="D9" s="18">
         <v>2</v>
       </c>
@@ -6357,7 +6380,7 @@
     </row>
     <row r="10" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="8"/>
-      <c r="C10" s="52"/>
+      <c r="C10" s="51"/>
       <c r="D10" s="8"/>
       <c r="E10" s="42"/>
       <c r="F10" s="8"/>
@@ -6387,7 +6410,7 @@
       <c r="B12" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="C12" s="51"/>
+      <c r="C12" s="53"/>
       <c r="D12" s="18">
         <v>3</v>
       </c>
@@ -6405,7 +6428,7 @@
       <c r="B13" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="C13" s="51"/>
+      <c r="C13" s="53"/>
       <c r="D13" s="18">
         <v>3</v>
       </c>
@@ -6423,7 +6446,7 @@
       <c r="B14" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="51"/>
+      <c r="C14" s="53"/>
       <c r="D14" s="18">
         <v>3</v>
       </c>
@@ -6439,7 +6462,7 @@
     </row>
     <row r="15" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="8"/>
-      <c r="C15" s="51"/>
+      <c r="C15" s="53"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
@@ -6447,7 +6470,7 @@
     </row>
     <row r="16" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="8"/>
-      <c r="C16" s="52"/>
+      <c r="C16" s="51"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
@@ -6477,7 +6500,7 @@
       <c r="B18" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="C18" s="51"/>
+      <c r="C18" s="53"/>
       <c r="D18" s="18">
         <v>5</v>
       </c>
@@ -6495,7 +6518,7 @@
       <c r="B19" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="C19" s="51"/>
+      <c r="C19" s="53"/>
       <c r="D19" s="18">
         <v>3</v>
       </c>
@@ -6513,7 +6536,7 @@
       <c r="B20" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="C20" s="51"/>
+      <c r="C20" s="53"/>
       <c r="D20" s="18">
         <v>4</v>
       </c>
@@ -6529,7 +6552,7 @@
     </row>
     <row r="21" spans="2:7" ht="15" x14ac:dyDescent="0.2">
       <c r="B21" s="8"/>
-      <c r="C21" s="51"/>
+      <c r="C21" s="53"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
@@ -6537,7 +6560,7 @@
     </row>
     <row r="22" spans="2:7" ht="15" x14ac:dyDescent="0.2">
       <c r="B22" s="8"/>
-      <c r="C22" s="52"/>
+      <c r="C22" s="51"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
@@ -8878,27 +8901,27 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C3" s="77" t="s">
+      <c r="C3" s="82" t="s">
         <v>139</v>
       </c>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="79"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="84"/>
       <c r="G3" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="H3" s="77" t="s">
+      <c r="H3" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="79"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="84"/>
     </row>
     <row r="4" spans="2:11" ht="13" x14ac:dyDescent="0.15">
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="72" t="s">
         <v>142</v>
       </c>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="74" t="s">
         <v>143</v>
       </c>
       <c r="D4" s="76" t="s">
@@ -8907,13 +8930,13 @@
       <c r="E4" s="76" t="s">
         <v>145</v>
       </c>
-      <c r="F4" s="83" t="s">
+      <c r="F4" s="77" t="s">
         <v>146</v>
       </c>
-      <c r="G4" s="72" t="s">
+      <c r="G4" s="79" t="s">
         <v>147</v>
       </c>
-      <c r="H4" s="74" t="s">
+      <c r="H4" s="81" t="s">
         <v>148</v>
       </c>
       <c r="I4" s="76" t="s">
@@ -8922,21 +8945,21 @@
       <c r="J4" s="76" t="s">
         <v>149</v>
       </c>
-      <c r="K4" s="83" t="s">
+      <c r="K4" s="77" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="13" x14ac:dyDescent="0.15">
-      <c r="B5" s="81"/>
+      <c r="B5" s="73"/>
       <c r="C5" s="75"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="73"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="80"/>
       <c r="H5" s="75"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="84"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="78"/>
     </row>
     <row r="6" spans="2:11" ht="15" x14ac:dyDescent="0.2">
       <c r="B6" s="46" t="s">
@@ -8958,12 +8981,9 @@
         <v>152</v>
       </c>
       <c r="H6" s="47" t="s">
-        <v>153</v>
-      </c>
-      <c r="I6" s="8">
-        <f>SUM(J6:K6)</f>
-        <v>0</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="I6" s="8"/>
       <c r="J6" s="8"/>
       <c r="K6" s="48"/>
     </row>
@@ -9949,11 +9969,6 @@
     <row r="1000" ht="13" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="I4:I5"/>
@@ -9961,6 +9976,11 @@
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="K4:K5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
